--- a/data/trans_orig/P46-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P46-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la opinión que tienen si tomasen el sol sin ninguna protección en 2007</t>
+          <t>Población según la opinión que tienen si tomasen el sol sin ninguna protección en 2007 (tasa de respuesta: 97,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32298</t>
+          <t>31583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60389</t>
+          <t>59353</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28737</t>
+          <t>27706</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46741</t>
+          <t>46220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79086</t>
+          <t>80090</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61187</t>
+          <t>61662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96358</t>
+          <t>96084</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27127</t>
+          <t>26164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53155</t>
+          <t>50920</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +895,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>115024</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>94239</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>136768</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>4,16%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>115024</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>97164</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>139062</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130965</t>
+          <t>133514</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177412</t>
+          <t>178511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44360</t>
+          <t>44378</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73000</t>
+          <t>72884</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>185349</t>
+          <t>182932</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>240802</t>
+          <t>237287</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>278599</t>
+          <t>278735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>334439</t>
+          <t>335112</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>362752</t>
+          <t>361179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>428571</t>
+          <t>428260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>654186</t>
+          <t>652603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>742521</t>
+          <t>743698</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185644</t>
+          <t>186082</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>236065</t>
+          <t>236767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361129</t>
+          <t>359028</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>428121</t>
+          <t>428213</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>564476</t>
+          <t>559919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>645107</t>
+          <t>645327</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173030</t>
+          <t>174101</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>224955</t>
+          <t>223885</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>344157</t>
+          <t>346495</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>406207</t>
+          <t>410464</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>535953</t>
+          <t>536859</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>622070</t>
+          <t>617175</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32738</t>
+          <t>32806</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60968</t>
+          <t>58734</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>27423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48247</t>
+          <t>47061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80905</t>
+          <t>78336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>127818</t>
+          <t>125836</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173430</t>
+          <t>174398</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72107</t>
+          <t>71938</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>107601</t>
+          <t>108336</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>209184</t>
+          <t>210266</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>269937</t>
+          <t>271657</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>251528</t>
+          <t>251549</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>315199</t>
+          <t>310564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116144</t>
+          <t>114152</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162989</t>
+          <t>160261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>384179</t>
+          <t>379177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>457647</t>
+          <t>462758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>558665</t>
+          <t>554356</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>636568</t>
+          <t>634015</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>535058</t>
+          <t>532468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>609183</t>
+          <t>609424</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1117141</t>
+          <t>1115856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1221841</t>
+          <t>1226150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>337943</t>
+          <t>335263</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>407272</t>
+          <t>404189</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>422602</t>
+          <t>424365</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>495639</t>
+          <t>496592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>778142</t>
+          <t>780526</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>878305</t>
+          <t>880216</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>187917</t>
+          <t>187175</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242885</t>
+          <t>241120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>264439</t>
+          <t>263704</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>328046</t>
+          <t>324239</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>462929</t>
+          <t>466570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>550167</t>
+          <t>551269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,62 +2357,62 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>10190</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2726</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>10526</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37340</t>
+          <t>36819</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21121</t>
+          <t>21662</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43380</t>
+          <t>45350</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39615</t>
+          <t>40814</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68115</t>
+          <t>68605</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>21160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44133</t>
+          <t>43511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>66594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102199</t>
+          <t>102498</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>199412</t>
+          <t>197149</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>244635</t>
+          <t>242770</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>151369</t>
+          <t>148485</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>191980</t>
+          <t>191459</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>361258</t>
+          <t>359240</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>424721</t>
+          <t>420755</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,89%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108515</t>
+          <t>109047</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152119</t>
+          <t>148890</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>127243</t>
+          <t>128710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>167428</t>
+          <t>166922</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>246839</t>
+          <t>247069</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>303488</t>
+          <t>305044</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89242</t>
+          <t>89037</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127534</t>
+          <t>128579</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96174</t>
+          <t>94855</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>133108</t>
+          <t>132780</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>198582</t>
+          <t>197023</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>250954</t>
+          <t>249900</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>75181</t>
+          <t>73122</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>113870</t>
+          <t>111827</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24924</t>
+          <t>23893</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50493</t>
+          <t>48570</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106978</t>
+          <t>104315</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>151387</t>
+          <t>151094</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>221938</t>
+          <t>219907</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>283652</t>
+          <t>283488</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110681</t>
+          <t>112099</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>157732</t>
+          <t>157954</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>346365</t>
+          <t>344247</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>418143</t>
+          <t>421936</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>448452</t>
+          <t>443392</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>533610</t>
+          <t>526992</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>195611</t>
+          <t>197043</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257398</t>
+          <t>257335</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>666790</t>
+          <t>665950</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>765628</t>
+          <t>769904</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1068094</t>
+          <t>1067727</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1177880</t>
+          <t>1176198</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1082666</t>
+          <t>1084373</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1191139</t>
+          <t>1195445</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2182093</t>
+          <t>2181801</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2337264</t>
+          <t>2332734</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>663014</t>
+          <t>665386</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>756519</t>
+          <t>754686</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>944716</t>
+          <t>943274</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1047075</t>
+          <t>1049437</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1636431</t>
+          <t>1638504</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1776460</t>
+          <t>1790945</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>477751</t>
+          <t>479518</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>561197</t>
+          <t>562080</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744355</t>
+          <t>742461</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>843269</t>
+          <t>841927</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1234904</t>
+          <t>1241573</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1367968</t>
+          <t>1369430</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la opinión que tienen si tomasen el sol sin ninguna protección en 2012</t>
+          <t>Población según la opinión que tienen si tomasen el sol sin ninguna protección en 2012 (tasa de respuesta: 98,05%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54657</t>
+          <t>54103</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89586</t>
+          <t>85414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28814</t>
+          <t>29766</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53611</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92236</t>
+          <t>92244</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136631</t>
+          <t>132749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127191</t>
+          <t>128203</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172567</t>
+          <t>172134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87935</t>
+          <t>87968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127356</t>
+          <t>128906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228767</t>
+          <t>229664</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290248</t>
+          <t>296010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131458</t>
+          <t>134849</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>179358</t>
+          <t>182260</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100228</t>
+          <t>100253</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143232</t>
+          <t>142279</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>246403</t>
+          <t>247007</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>309846</t>
+          <t>310140</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4482,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164727</t>
+          <t>165160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>219979</t>
+          <t>216905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>244028</t>
+          <t>242455</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>304719</t>
+          <t>302828</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>420291</t>
+          <t>421938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>501165</t>
+          <t>498764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154853</t>
+          <t>153151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203851</t>
+          <t>204942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>328494</t>
+          <t>328952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>396129</t>
+          <t>392106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>497741</t>
+          <t>503200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>587212</t>
+          <t>583317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4708,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>182824</t>
+          <t>178334</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>236281</t>
+          <t>232508</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>338694</t>
+          <t>339337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>408170</t>
+          <t>407564</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>532304</t>
+          <t>531153</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>618893</t>
+          <t>614928</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73741</t>
+          <t>74463</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112780</t>
+          <t>112377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42953</t>
+          <t>41848</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73762</t>
+          <t>73162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123685</t>
+          <t>125130</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173417</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>200737</t>
+          <t>199173</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>260767</t>
+          <t>257773</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121619</t>
+          <t>122777</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>169964</t>
+          <t>169098</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>339275</t>
+          <t>339160</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>414754</t>
+          <t>418855</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>280590</t>
+          <t>281741</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>350626</t>
+          <t>347771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>168614</t>
+          <t>164003</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220301</t>
+          <t>220037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>461858</t>
+          <t>465152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>548856</t>
+          <t>551428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>522537</t>
+          <t>529389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607061</t>
+          <t>609016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>399037</t>
+          <t>399684</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>474455</t>
+          <t>470588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>949490</t>
+          <t>946040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1057723</t>
+          <t>1057763</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>358523</t>
+          <t>358069</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>433652</t>
+          <t>431962</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>425768</t>
+          <t>427826</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>504935</t>
+          <t>499594</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>800131</t>
+          <t>800932</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>910452</t>
+          <t>908429</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -5503,12 +5503,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>316142</t>
+          <t>313726</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>382572</t>
+          <t>381235</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>403668</t>
+          <t>405711</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>478709</t>
+          <t>479308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>745671</t>
+          <t>738591</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>843332</t>
+          <t>840338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -5733,12 +5733,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>21296</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>12376</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30575</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21283</t>
+          <t>20621</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45012</t>
+          <t>44138</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45553</t>
+          <t>44043</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>46505</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80500</t>
+          <t>79573</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -5959,12 +5959,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51204</t>
+          <t>50795</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82091</t>
+          <t>82478</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45867</t>
+          <t>47289</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>79473</t>
+          <t>79635</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6009,12 +6009,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104071</t>
+          <t>107089</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>149812</t>
+          <t>152553</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -6072,12 +6072,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>141340</t>
+          <t>139399</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>185527</t>
+          <t>185011</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100423</t>
+          <t>97636</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>141121</t>
+          <t>136466</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6142,12 +6142,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>254618</t>
+          <t>249476</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>311356</t>
+          <t>310076</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96066</t>
+          <t>97359</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135920</t>
+          <t>136555</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99355</t>
+          <t>98402</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138237</t>
+          <t>138771</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>205880</t>
+          <t>205306</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>265319</t>
+          <t>263944</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72444</t>
+          <t>72822</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>110196</t>
+          <t>109885</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6333,12 +6333,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>101244</t>
+          <t>102769</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144049</t>
+          <t>141433</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>186640</t>
+          <t>184866</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>241796</t>
+          <t>239898</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>149845</t>
+          <t>148239</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>204709</t>
+          <t>200251</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84229</t>
+          <t>84570</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>125157</t>
+          <t>126290</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>245811</t>
+          <t>248805</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>312077</t>
+          <t>314568</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>370692</t>
+          <t>370993</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>450448</t>
+          <t>449084</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>246734</t>
+          <t>248560</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>316161</t>
+          <t>315063</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>640982</t>
+          <t>644638</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>746320</t>
+          <t>741857</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>492041</t>
+          <t>487834</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>580303</t>
+          <t>574419</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6789,12 +6789,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>342912</t>
+          <t>340877</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>417692</t>
+          <t>416750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>855221</t>
+          <t>851261</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>970149</t>
+          <t>967391</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>864245</t>
+          <t>870757</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>972475</t>
+          <t>971985</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6882,12 +6882,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>775668</t>
+          <t>771509</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>880068</t>
+          <t>874538</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1669906</t>
+          <t>1671680</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1819206</t>
+          <t>1823094</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -6980,12 +6980,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>640744</t>
+          <t>646207</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>738098</t>
+          <t>738305</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>884784</t>
+          <t>889041</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>993529</t>
+          <t>995128</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1555742</t>
+          <t>1559321</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1699715</t>
+          <t>1700876</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>595271</t>
+          <t>594258</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>688277</t>
+          <t>686979</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>880542</t>
+          <t>872994</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>985067</t>
+          <t>986881</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1510285</t>
+          <t>1509960</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1660916</t>
+          <t>1656321</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la opinión que tienen si tomasen el sol sin ninguna protección en 2016</t>
+          <t>Población según la opinión que tienen si tomasen el sol sin ninguna protección en 2016 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41355</t>
+          <t>40033</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36673</t>
+          <t>37847</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42166</t>
+          <t>41368</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72537</t>
+          <t>72031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -7667,12 +7667,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66143</t>
+          <t>68113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99236</t>
+          <t>101479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37227</t>
+          <t>36532</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65611</t>
+          <t>63828</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109351</t>
+          <t>111273</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153626</t>
+          <t>153186</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>137092</t>
+          <t>134600</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>178022</t>
+          <t>178433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85223</t>
+          <t>84807</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125819</t>
+          <t>124963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>232765</t>
+          <t>234874</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>292086</t>
+          <t>291759</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -7893,12 +7893,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175520</t>
+          <t>174465</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>221016</t>
+          <t>220569</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7928,12 +7928,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>241127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>298402</t>
+          <t>299667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>435722</t>
+          <t>432445</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>508766</t>
+          <t>506370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -8006,12 +8006,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121875</t>
+          <t>120334</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163306</t>
+          <t>164798</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>250205</t>
+          <t>252081</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305329</t>
+          <t>309879</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>381498</t>
+          <t>381132</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>455529</t>
+          <t>453796</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>109781</t>
+          <t>110466</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>151737</t>
+          <t>151584</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>222598</t>
+          <t>225137</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>280006</t>
+          <t>282542</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>347094</t>
+          <t>343223</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>416835</t>
+          <t>419355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92046</t>
+          <t>90643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>131646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8384,12 +8384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>29000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52472</t>
+          <t>53357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126885</t>
+          <t>126548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175230</t>
+          <t>176929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -8462,12 +8462,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>169964</t>
+          <t>169012</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>225084</t>
+          <t>225099</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85893</t>
+          <t>85800</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>127317</t>
+          <t>125851</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>269250</t>
+          <t>264978</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>339005</t>
+          <t>335685</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>339949</t>
+          <t>340236</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>415588</t>
+          <t>409899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>174215</t>
+          <t>175183</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232344</t>
+          <t>231540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>531094</t>
+          <t>531744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>620852</t>
+          <t>620452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -8688,12 +8688,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609692</t>
+          <t>612291</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>698124</t>
+          <t>700246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>627324</t>
+          <t>625813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>714830</t>
+          <t>710413</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1260884</t>
+          <t>1265512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1381184</t>
+          <t>1385970</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -8801,12 +8801,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>379626</t>
+          <t>374724</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>454358</t>
+          <t>451644</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>495059</t>
+          <t>497263</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>573919</t>
+          <t>577677</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8871,12 +8871,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>898605</t>
+          <t>896118</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1007176</t>
+          <t>1009515</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8886,12 +8886,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -8914,12 +8914,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>272105</t>
+          <t>270732</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>339008</t>
+          <t>333724</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>395768</t>
+          <t>398275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>471332</t>
+          <t>471254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>685755</t>
+          <t>687052</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>786286</t>
+          <t>787335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8999,12 +8999,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -9144,12 +9144,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34046</t>
+          <t>32040</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21124</t>
+          <t>22176</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24290</t>
+          <t>24279</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48592</t>
+          <t>48434</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -9257,12 +9257,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29777</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54489</t>
+          <t>53057</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9272,12 +9272,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26162</t>
+          <t>26636</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50112</t>
+          <t>51666</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61144</t>
+          <t>59359</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97022</t>
+          <t>95238</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -9370,12 +9370,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59439</t>
+          <t>60255</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93319</t>
+          <t>93912</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43357</t>
+          <t>43014</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70036</t>
+          <t>70266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9420,12 +9420,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111724</t>
+          <t>110374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>154584</t>
+          <t>154534</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>154043</t>
+          <t>155122</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>199240</t>
+          <t>198019</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>137411</t>
+          <t>136787</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181176</t>
+          <t>178429</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>304263</t>
+          <t>305212</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>366418</t>
+          <t>366226</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -9596,12 +9596,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111397</t>
+          <t>111232</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153444</t>
+          <t>150471</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125444</t>
+          <t>126516</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166630</t>
+          <t>166348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>246160</t>
+          <t>247407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>304346</t>
+          <t>306885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9681,12 +9681,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -9709,12 +9709,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>81544</t>
+          <t>81191</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117550</t>
+          <t>119564</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>117245</t>
+          <t>116868</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>159993</t>
+          <t>159018</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9759,12 +9759,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>208813</t>
+          <t>211829</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>266830</t>
+          <t>269476</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -9939,12 +9939,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>137731</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>190153</t>
+          <t>192439</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9974,12 +9974,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62302</t>
+          <t>60930</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97394</t>
+          <t>96562</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>210121</t>
+          <t>209832</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>272643</t>
+          <t>271042</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -10052,12 +10052,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>282081</t>
+          <t>283480</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>353680</t>
+          <t>351929</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>166613</t>
+          <t>165433</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>220405</t>
+          <t>222082</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10102,12 +10102,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>464551</t>
+          <t>467983</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>553441</t>
+          <t>556496</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>562803</t>
+          <t>564925</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>652045</t>
+          <t>653918</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>329243</t>
+          <t>325573</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>402212</t>
+          <t>397460</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>915258</t>
+          <t>914040</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1027093</t>
+          <t>1027562</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -10278,12 +10278,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>975638</t>
+          <t>976700</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1081545</t>
+          <t>1083564</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10293,12 +10293,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1040048</t>
+          <t>1043953</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1155312</t>
+          <t>1153482</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10328,12 +10328,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2046201</t>
+          <t>2048250</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2200057</t>
+          <t>2203421</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10363,12 +10363,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>634468</t>
+          <t>639962</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>733391</t>
+          <t>734120</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>906399</t>
+          <t>908613</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1010185</t>
+          <t>1015631</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1578617</t>
+          <t>1568338</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1721513</t>
+          <t>1716878</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10476,12 +10476,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -10504,12 +10504,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>489668</t>
+          <t>489772</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>579488</t>
+          <t>580112</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>766946</t>
+          <t>772069</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>871361</t>
+          <t>871722</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10574,12 +10574,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1289043</t>
+          <t>1294374</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1423775</t>
+          <t>1423747</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
